--- a/octubre_lleno.xlsx
+++ b/octubre_lleno.xlsx
@@ -111,6 +111,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E2FECD"/>
+        <bgColor rgb="00E2FECD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C9C9C9"/>
         <bgColor rgb="00C9C9C9"/>
       </patternFill>
@@ -119,12 +125,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00ABFBFE"/>
         <bgColor rgb="00ABFBFE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2FECD"/>
-        <bgColor rgb="00E2FECD"/>
       </patternFill>
     </fill>
     <fill>
@@ -297,33 +297,33 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -632,20 +632,20 @@
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="1" t="n"/>
       <c r="F2" s="2" t="n"/>
-      <c r="G2" s="23" t="inlineStr">
-        <is>
-          <t>Miércoles 1 (8h 15m)</t>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Miércoles 1 (2h 30m)</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Jueves 2 (7h)</t>
+          <t>Jueves 2 (2h)</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>Viernes 3 (5h)</t>
+          <t>Viernes 3 (30m)</t>
         </is>
       </c>
     </row>
@@ -658,333 +658,235 @@
     </row>
     <row r="4">
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="24" t="n"/>
+      <c r="D4" s="23" t="n"/>
       <c r="E4" s="5" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="26" t="inlineStr">
-        <is>
-          <t>Publicar - None - CAMANBET - 60 
- https://camanbet.com/deportes/67 
+      <c r="F4" s="24" t="n"/>
+      <c r="G4" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - DORADOBET CR - 15 
+ https://doradobet.com/deportes/80                Unihockey 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
       <c r="H4" s="17" t="n"/>
-      <c r="I4" s="27" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ACIERTALA - 45 
- ADT vs Sporting Cristal 10/4/2025 Liga 1 Perú 
-Responsable hacer: Manuela 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="K4" s="27" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ACIERTALA - 120 
- Partido Juventus vs AC Milán (Derby del Nord-Ovest) Liga Italiana 10/5/2025 
-Responsable hacer: Manuela 
+      <c r="I4" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET GT - 30 
+ Liga de Guatemala - Comunicaciones vs Municipal y Antigua vs Xelajú (5/10/2025) 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="K4" s="26" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ECUABET - 30 
+ Torneo deportivo 1 - Torneo E-sports (4/10/2025 - 30/10/2025) 
+Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="28" t="n"/>
+      <c r="D5" s="27" t="n"/>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="28" t="n"/>
-      <c r="G5" s="26" t="inlineStr">
-        <is>
-          <t>Publicar - None - CAMANBET - 45 
- Sorteo la Guardinga  
-Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="H5" s="28" t="n"/>
-      <c r="I5" s="27" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ACIERTALA - 120 
- Chelsea vs Liverpool Liga Inglesa 10/4/2025 
-Responsable hacer: Manuela 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="K5" s="26" t="inlineStr">
-        <is>
-          <t>Publicar - None - CAMANBET - 90 
- Ultima Fecha de la liga de venezuela 10/5/2025 
-Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
+      <c r="F5" s="27" t="n"/>
+      <c r="G5" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET CR - 30 
+ Bono deposito casino - Giros por Sinpe (1/10/2025 - 29/10/2025) 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="H5" s="27" t="n"/>
+      <c r="I5" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET PE - 30 
+ Liga 1 Perú - ADT vs Sporting Cristal (4/10/2025) 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="C6" s="5" t="n"/>
-      <c r="D6" s="28" t="n"/>
+      <c r="D6" s="27" t="n"/>
       <c r="E6" s="5" t="n"/>
-      <c r="F6" s="28" t="n"/>
-      <c r="G6" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - DORADOBET CR - 30 
- https://doradobet.com/deportes/80                Unihockey 
-Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="H6" s="28" t="n"/>
-      <c r="I6" s="27" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ACIERTALA - 30 
- ufc 320- Magomed Ankalaev -AlexPereira UFC 10/4/2025 
-Responsable hacer: Manuela 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="K6" s="30" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ECUABET - 60 
- Torneo deportivo 1 - Torneo E-sports (4/10/2025 - 30/10/2025) 
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
+      <c r="F6" s="27" t="n"/>
+      <c r="G6" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - DORADOBET GT - 15 
+ https://doradobet.com/deportes/93                                        Biatlón 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="H6" s="27" t="n"/>
+      <c r="I6" s="26" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ECUABET - 30 
+ Liga inglesa: Chelsea vs Liverpool (4/10/2025) 
+Responsable hacer: juan manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="28" t="n"/>
+      <c r="D7" s="27" t="n"/>
       <c r="E7" s="5" t="n"/>
-      <c r="F7" s="28" t="n"/>
-      <c r="G7" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET CR - 45 
- Bono deposito casino - Giros por Sinpe (1/10/2025 - 29/10/2025) 
-Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="H7" s="28" t="n"/>
-      <c r="I7" s="29" t="inlineStr">
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>Publicar - Blog - DORADOBET GT - 30 
- Liga de Guatemala - Comunicaciones vs Municipal y Antigua vs Xelajú (5/10/2025) 
-Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="K7" s="30" t="inlineStr">
-        <is>
-          <t>Hacer - Plataforma - ECUABET - 30 
- https://ecuabet.com/politica-de-privacidad  
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
+ Torneo casino - Torneo Slot (1/10/2025 - 29/10/2025) 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="H7" s="27" t="n"/>
+      <c r="I7" s="26" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ECUABET - 30 
+ UFC 320 - Magomed Ankalaev - AlexPereira (4/10/2025) 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="28" t="n"/>
+      <c r="D8" s="27" t="n"/>
       <c r="E8" s="5" t="n"/>
-      <c r="F8" s="28" t="n"/>
-      <c r="G8" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - DORADOBET GT - 60 
- https://doradobet.com/deportes/93                                        Biatlón 
-Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="H8" s="28" t="n"/>
-      <c r="I8" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET PE - 60 
- Liga 1 Perú - ADT vs Sporting Cristal (4/10/2025) 
-Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
+      <c r="F8" s="27" t="n"/>
+      <c r="G8" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - DORADOBET PE - 15 
+ https://doradobet.com/pe/casino-en-vivo 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="H8" s="27" t="n"/>
+      <c r="I8" s="5" t="n"/>
       <c r="K8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="28" t="n"/>
+      <c r="D9" s="27" t="n"/>
       <c r="E9" s="5" t="n"/>
-      <c r="F9" s="28" t="n"/>
-      <c r="G9" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET GT - 60 
- Torneo casino - Torneo Slot (1/10/2025 - 29/10/2025) 
-Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="H9" s="28" t="n"/>
-      <c r="I9" s="30" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ECUABET - 30 
- Liga inglesa: Chelsea vs Liverpool (4/10/2025) 
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
+      <c r="F9" s="27" t="n"/>
+      <c r="G9" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET PE - 30 
+ Premios misteriorsos con Playtech - jueves de premios (2/10/25 - 30/10/2025) 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="H9" s="27" t="n"/>
+      <c r="I9" s="5" t="n"/>
       <c r="K9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="28" t="n"/>
+      <c r="D10" s="27" t="n"/>
       <c r="E10" s="5" t="n"/>
-      <c r="F10" s="28" t="n"/>
-      <c r="G10" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - DORADOBET PE - 15 
- https://doradobet.com/pe/casino-en-vivo 
-Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="H10" s="28" t="n"/>
-      <c r="I10" s="30" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ECUABET - 15 
- UFC 320 - Magomed Ankalaev - AlexPereira (4/10/2025) 
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
+      <c r="F10" s="27" t="n"/>
+      <c r="G10" s="26" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - ECUABET - 15 
+ https://ecuabet.com/new-casino/categoria/nuevos-752 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="H10" s="27" t="n"/>
+      <c r="I10" s="5" t="n"/>
       <c r="K10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="28" t="n"/>
+      <c r="D11" s="27" t="n"/>
       <c r="E11" s="5" t="n"/>
-      <c r="F11" s="28" t="n"/>
-      <c r="G11" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET PE - 30 
- Premios misteriorsos con Playtech - jueves de premios (2/10/25 - 30/10/2025) 
-Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="H11" s="28" t="n"/>
-      <c r="I11" s="30" t="inlineStr">
-        <is>
-          <t>Hacer - Plataforma - ECUABET - 30 
- https://ecuabet.com/trabaja-con-nosotros  
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
+      <c r="F11" s="27" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="27" t="n"/>
+      <c r="I11" s="5" t="n"/>
       <c r="K11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="28" t="n"/>
+      <c r="D12" s="27" t="n"/>
       <c r="E12" s="5" t="n"/>
-      <c r="F12" s="28" t="n"/>
-      <c r="G12" s="30" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - ECUABET - 30 
- https://ecuabet.com/new-casino/categoria/nuevos-752 
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="H12" s="28" t="n"/>
-      <c r="I12" s="30" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - ECUABET - 60 
- Torneo deportivo 1 - Torneo E-sports (4/10/2025 - 30/10/2025)  
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
+      <c r="F12" s="27" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="27" t="n"/>
+      <c r="I12" s="5" t="n"/>
       <c r="K12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="28" t="n"/>
+      <c r="D13" s="27" t="n"/>
       <c r="E13" s="5" t="n"/>
-      <c r="F13" s="28" t="n"/>
-      <c r="G13" s="30" t="inlineStr">
-        <is>
-          <t>Hacer - Plataforma - ECUABET - 60 
- https://ecuabet.com/new-casino/categoria/populares-241  
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="H13" s="28" t="n"/>
+      <c r="F13" s="27" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="27" t="n"/>
       <c r="I13" s="5" t="n"/>
       <c r="K13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="28" t="n"/>
+      <c r="D14" s="27" t="n"/>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="28" t="n"/>
-      <c r="G14" s="30" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - ECUABET - 30 
- Liga inglesa: Chelsea vs Liverpool (4/10/2025)  
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="H14" s="28" t="n"/>
+      <c r="F14" s="27" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="27" t="n"/>
       <c r="I14" s="5" t="n"/>
       <c r="K14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="28" t="n"/>
+      <c r="D15" s="27" t="n"/>
       <c r="E15" s="5" t="n"/>
-      <c r="F15" s="28" t="n"/>
-      <c r="G15" s="30" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - ECUABET - 15 
- UFC 320 - Magomed Ankalaev - AlexPereira (4/10/2025)  
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="H15" s="28" t="n"/>
+      <c r="F15" s="27" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="27" t="n"/>
       <c r="I15" s="5" t="n"/>
       <c r="K15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="28" t="n"/>
+      <c r="D16" s="27" t="n"/>
       <c r="E16" s="5" t="n"/>
-      <c r="F16" s="28" t="n"/>
-      <c r="G16" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - DORADOBET SV - 15 
- https://doradobet.sv/new-casino/proveedor/PAHACKSAW 
-Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="H16" s="28" t="n"/>
+      <c r="F16" s="27" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="27" t="n"/>
       <c r="I16" s="5" t="n"/>
       <c r="K16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="C17" s="5" t="n"/>
-      <c r="D17" s="28" t="n"/>
+      <c r="D17" s="27" t="n"/>
       <c r="E17" s="5" t="n"/>
-      <c r="F17" s="28" t="n"/>
+      <c r="F17" s="27" t="n"/>
       <c r="G17" s="5" t="n"/>
-      <c r="H17" s="28" t="n"/>
+      <c r="H17" s="27" t="n"/>
       <c r="I17" s="5" t="n"/>
       <c r="K17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="31" t="n"/>
+      <c r="D18" s="28" t="n"/>
       <c r="E18" s="5" t="n"/>
-      <c r="F18" s="31" t="n"/>
+      <c r="F18" s="28" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="28" t="n"/>
+      <c r="H18" s="27" t="n"/>
       <c r="I18" s="5" t="n"/>
       <c r="K18" s="5" t="n"/>
     </row>
@@ -1007,93 +909,51 @@
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>Lunes 6 (4h 15m)</t>
+          <t>Lunes 6 (30m)</t>
         </is>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>Martes 7 (2h 45m)</t>
+          <t>Martes 7 (1h 30m)</t>
         </is>
       </c>
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Miércoles 8 (3h 15m)</t>
+          <t>Miércoles 8 (2h)</t>
         </is>
       </c>
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Jueves 9 (1h)</t>
+          <t>Jueves 9 (0h)</t>
         </is>
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>Viernes 10 (5h 15m)</t>
+          <t>Viernes 10 (2h)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="26" t="inlineStr">
-        <is>
-          <t>Publicar - None - CAMANBET - 180 
- Guia para ganar con los Crash Games 
-Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="E22" s="27" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ACIERTALA - 30 
- Guía para apostar en Esports 
-Responsable hacer: Manuela 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="G22" s="27" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ACIERTALA - 45 
- ¿Cómo hacer apuestas de básquet? 
-Responsable hacer: Manuela 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="I22" s="30" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - ECUABET - 60 
- Guía bingo online  
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="K22" s="26" t="inlineStr">
-        <is>
-          <t>Publicar - None - CAMANBET - 60 
- https://camanbet.com/new-casino/categoria/Bingos-1441 
-Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET PE - 60 
+      <c r="C22" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET PE - 30 
  Juegos de Playtech 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="E23" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET CR - 60 
+      <c r="E22" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET CR - 30 
  Guía de Super 7s 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="G23" s="29" t="inlineStr">
+      <c r="G22" s="25" t="inlineStr">
         <is>
           <t>Publicar - Blog - DORADOBET CR - 30 
  Honduras vs Costa Rica - Eliminatorias Concacaf (9/10/2025) 
@@ -1101,26 +961,19 @@
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="I23" s="5" t="n"/>
-      <c r="K23" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - DORADOBET CR - 60 
+      <c r="I22" s="5" t="n"/>
+      <c r="K22" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - DORADOBET CR - 15 
  https://doradobet.com/deportes/85                Golf 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="C24" s="30" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - ECUABET - 15 
- Amistoso Estados Unidos vs Ecuador (10/10/25)  
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="E24" s="29" t="inlineStr">
+    <row r="23">
+      <c r="C23" s="5" t="n"/>
+      <c r="E23" s="25" t="inlineStr">
         <is>
           <t>Publicar - Blog - DORADOBET GT - 30 
  Eliminatorias Concacaf - Surinam vs Guatemala (10/10/2025) 
@@ -1128,19 +981,47 @@
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="G24" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET GT - 60 
+      <c r="G23" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET GT - 30 
  Guía de juegos Piggy Coins 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
+      <c r="I23" s="5" t="n"/>
+      <c r="K23" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET CR - 30 
+ Haití vs Costa Rica - Eliminatorias Concacaf (13/10/2025) 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" s="5" t="n"/>
+      <c r="E24" s="26" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ECUABET - 30 
+ Amistoso Estados Unidos vs Ecuador (10/10/25) 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="G24" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET PE - 30 
+ Guía de BlackJack 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
       <c r="I24" s="5" t="n"/>
-      <c r="K24" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET CR - 15 
- Haití vs Costa Rica - Eliminatorias Concacaf (13/10/2025) 
+      <c r="K24" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - DORADOBET GT - 15 
+ https://doradobet.com/deportes/106                                        Fútbol Australiano 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
@@ -1148,27 +1029,20 @@
     </row>
     <row r="25">
       <c r="C25" s="5" t="n"/>
-      <c r="E25" s="30" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ECUABET - 15 
- Amistoso Estados Unidos vs Ecuador (10/10/25) 
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="G25" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET PE - 30 
- Guía de BlackJack 
+      <c r="E25" s="5" t="n"/>
+      <c r="G25" s="26" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ECUABET - 30 
+ Guía apuestas en Dota 2 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
       <c r="I25" s="5" t="n"/>
-      <c r="K25" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - DORADOBET GT - 15 
- https://doradobet.com/deportes/106                                        Fútbol Australiano 
+      <c r="K25" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - DORADOBET PE - 15 
+ https://doradobet.com/pe/new-casino/categoria/ruleta-11 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
@@ -1176,27 +1050,13 @@
     </row>
     <row r="26">
       <c r="C26" s="5" t="n"/>
-      <c r="E26" s="30" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - ECUABET - 30 
- Guía apuestas en Dota 2  
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="G26" s="30" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ECUABET - 30 
- Guía apuestas en Dota 2 
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
+      <c r="E26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
       <c r="I26" s="5" t="n"/>
-      <c r="K26" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - DORADOBET PE - 15 
- https://doradobet.com/pe/new-casino/categoria/ruleta-11 
+      <c r="K26" s="26" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - ECUABET - 15 
+ https://ecuabet.com/new-casino/categoria/populares-241 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
@@ -1207,11 +1067,11 @@
       <c r="E27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
       <c r="I27" s="5" t="n"/>
-      <c r="K27" s="30" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - ECUABET - 60 
- https://ecuabet.com/new-casino/categoria/populares-241 
-Responsable hacer: Santiago 
+      <c r="K27" s="26" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ECUABET - 30 
+ Guía bingo online 
+Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
@@ -1221,28 +1081,14 @@
       <c r="E28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
       <c r="I28" s="5" t="n"/>
-      <c r="K28" s="30" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ECUABET - 60 
- Guía bingo online 
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
+      <c r="K28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="C29" s="5" t="n"/>
       <c r="E29" s="5" t="n"/>
       <c r="G29" s="5" t="n"/>
       <c r="I29" s="5" t="n"/>
-      <c r="K29" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - DORADOBET SV - 30 
- https://doradobet.sv/deportes/107        Hockey sobre césped 
-Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
+      <c r="K29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="C30" s="5" t="n"/>
@@ -1302,129 +1148,108 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>Lunes 13 (3h)</t>
+          <t>Lunes 13 (1h)</t>
         </is>
       </c>
       <c r="D38" s="2" t="n"/>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>Martes 14 (15m)</t>
+          <t>Martes 14 (0h)</t>
         </is>
       </c>
       <c r="F38" s="2" t="n"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Miércoles 15 (15m)</t>
+          <t>Miércoles 15 (30m)</t>
         </is>
       </c>
       <c r="H38" s="2" t="n"/>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>Jueves 16 (3h 30m)</t>
+          <t>Jueves 16 (1h 30m)</t>
         </is>
       </c>
       <c r="K38" s="1" t="inlineStr">
         <is>
-          <t>Viernes 17 (6h 15m)</t>
+          <t>Viernes 17 (2h)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="C39" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET GT - 120 
+      <c r="C39" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET GT - 30 
  Eliminatorias Concacaf - El Salvador vs Guatemala (14/10/2025) 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
       <c r="D39" s="9" t="n"/>
-      <c r="E39" s="30" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - ECUABET - 15 
- ¿Qué son los pronósticos en vivo?  
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="G39" s="30" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ECUABET - 15 
+      <c r="E39" s="5" t="n"/>
+      <c r="G39" s="26" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ECUABET - 30 
  ¿Qué son los pronósticos en vivo? 
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="I39" s="27" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ACIERTALA - 60 
- Inicio de temporada de NBA 21/10/2025 
-Responsable hacer: Manuela 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="K39" s="27" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ACIERTALA - 15 
- Jornada 3 Champions 21-22 10/23/2025 
-Responsable hacer: Manuela 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="I39" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET CR - 30 
+ Alajuelense vs Saprissa - Liga de Costa Rica (18/10/2025) 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="K39" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET CR - 30 
+ Inicio de temporada NBA (21/10/2025) 
+Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="30" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - ECUABET - 30 
- Amistoso México vs Ecuador (14/10/25)  
-Responsable hacer: Santiago 
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ECUABET - 30 
+ Amistoso México vs Ecuador (14/10/25) 
+Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
       <c r="D40" s="10" t="n"/>
       <c r="E40" s="5" t="n"/>
       <c r="G40" s="5" t="n"/>
-      <c r="I40" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET CR - 120 
- Alajuelense vs Saprissa - Liga de Costa Rica (18/10/2025) 
-Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="K40" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET CR - 30 
- Inicio de temporada NBA (21/10/2025) 
+      <c r="I40" s="26" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - ECUABET - 60 
+ Inicio de temporada de NBA (21/10/2025)  
+Responsable hacer: Santiago 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="K40" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET GT - 30 
+ Central American Cup - semifinales de ida (21/10/2025 - 23/10/2025) 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="C41" s="30" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ECUABET - 30 
- Amistoso México vs Ecuador (14/10/25) 
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
+      <c r="C41" s="5" t="n"/>
       <c r="D41" s="10" t="n"/>
       <c r="E41" s="5" t="n"/>
       <c r="G41" s="5" t="n"/>
-      <c r="I41" s="30" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - ECUABET - 30 
- Inicio de temporada de NBA (21/10/2025)  
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="K41" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET GT - 180 
- Central American Cup - semifinales de ida (21/10/2025 - 23/10/2025) 
+      <c r="I41" s="5" t="n"/>
+      <c r="K41" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET PE - 30 
+ Jornada 3 Champions League (21/10/2025 - 22/10/2025) 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
@@ -1436,11 +1261,11 @@
       <c r="E42" s="5" t="n"/>
       <c r="G42" s="5" t="n"/>
       <c r="I42" s="5" t="n"/>
-      <c r="K42" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET PE - 60 
- Jornada 3 Champions League (21/10/2025 - 22/10/2025) 
-Responsable hacer: Juan Manuel 
+      <c r="K42" s="26" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ECUABET - 30 
+ Inicio de temporada de NBA (21/10/2025) 
+Responsable hacer: Santiago 
  Responsable publicar: Santiago</t>
         </is>
       </c>
@@ -1451,14 +1276,7 @@
       <c r="E43" s="5" t="n"/>
       <c r="G43" s="5" t="n"/>
       <c r="I43" s="5" t="n"/>
-      <c r="K43" s="30" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ECUABET - 30 
- Inicio de temporada de NBA (21/10/2025) 
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
+      <c r="K43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="C44" s="5" t="n"/>
@@ -1466,14 +1284,7 @@
       <c r="E44" s="5" t="n"/>
       <c r="G44" s="5" t="n"/>
       <c r="I44" s="5" t="n"/>
-      <c r="K44" s="30" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - ECUABET - 60 
- Jornada 3 Champions League (21/10/2025 - 22/10/2025)  
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
+      <c r="K44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="C45" s="5" t="n"/>
@@ -1555,51 +1366,44 @@
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>Lunes 20 (5h 30m)</t>
+          <t>Lunes 20 (1h 45m)</t>
         </is>
       </c>
       <c r="D55" s="2" t="n"/>
       <c r="E55" s="1" t="inlineStr">
         <is>
-          <t>Martes 21 (30m)</t>
+          <t>Martes 21 (0h)</t>
         </is>
       </c>
       <c r="F55" s="2" t="n"/>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>Miércoles 22 (1h 15m)</t>
+          <t>Miércoles 22 (1h)</t>
         </is>
       </c>
       <c r="H55" s="2" t="n"/>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Jueves 23 (3h 15m)</t>
+          <t>Jueves 23 (1h 30m)</t>
         </is>
       </c>
       <c r="K55" s="1" t="inlineStr">
         <is>
-          <t>Viernes 24 (4h 15m)</t>
+          <t>Viernes 24 (2h)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="C56" s="26" t="inlineStr">
-        <is>
-          <t>Publicar - None - CAMANBET - 30 
- https://camanbet.com/new-casino/proveedor/CALETA 
-Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="E56" s="30" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - ECUABET - 30 
- UFC 321- TomAspinall - CirylGane (25/10/2025)  
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="G56" s="29" t="inlineStr">
+      <c r="C56" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - DORADOBET CR - 15 
+ https://doradobet.com/new-casino/proveedor/PFBM 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n"/>
+      <c r="G56" s="25" t="inlineStr">
         <is>
           <t>Publicar - Blog - DORADOBET CR - 30 
  UFC 321- TomAspinall vs CirylGane (25/10/2025) 
@@ -1607,214 +1411,151 @@
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="I56" s="27" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ACIERTALA - 45 
- Guí de blackjack 
-Responsable hacer: Manuela 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="K56" s="27" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ACIERTALA - 90 
- Gp de México F1 10/26/2025 
-Responsable hacer: Manuela 
+      <c r="I56" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET PE - 30 
+ F1 - GP México (26/10/2025) 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="K56" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET GT - 30 
+ F1 Gp México (26/10/2025) 
+Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="C57" s="26" t="inlineStr">
-        <is>
-          <t>Publicar - None - CAMANBET - 15 
- Inicio de temporada de la NBA - 10/21/2025 
+      <c r="C57" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET CR - 30 
+ Partidos de Ida semifinales Central American Cup (21/10/2025 - 23/10/2025) 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
       <c r="E57" s="5" t="n"/>
-      <c r="G57" s="30" t="inlineStr">
+      <c r="G57" s="26" t="inlineStr">
         <is>
           <t>Publicar - Blog - ECUABET - 30 
  UFC 321- TomAspinall - CirylGane (25/10/2025) 
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="I57" s="27" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ACIERTALA - 60 
- 26/10/2025 Clasico Barcelona vs Real Madrid Liga española 
-Responsable hacer: Manuela 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="K57" s="26" t="inlineStr">
-        <is>
-          <t>Publicar - None - CAMANBET - 60 
- Clasico Barcelona vs Real Madrid - Liga Española - 10/26/2025 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="I57" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET PE - 30 
+ UFC 321- TomAspinall vs CirylGane (25/10/2025) 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="K57" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET GT - 30 
+ Liga española - Clasico Barcelona vs Real Madrid (26/10/2025) 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="C58" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - DORADOBET CR - 15 
- https://doradobet.com/new-casino/proveedor/PFBM 
+      <c r="C58" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - DORADOBET GT - 0 
+ https://doradobet.com/gt/new-casino/categoria/tragamonedas-513                                 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
       <c r="E58" s="5" t="n"/>
-      <c r="G58" s="30" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - ECUABET - 15 
- Liga española: clasico Barcelona vs Real Madrid (26/10/25)  
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="I58" s="29" t="inlineStr">
+      <c r="G58" s="5" t="n"/>
+      <c r="I58" s="26" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ECUABET - 30 
+ Liga española: clasico Barcelona vs Real Madrid (26/10/25) 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="K58" s="25" t="inlineStr">
         <is>
           <t>Publicar - Blog - DORADOBET PE - 30 
- F1 - GP México (26/10/2025) 
-Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="K58" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET GT - 30 
- F1 Gp México (26/10/2025) 
+ Liga española - Clasico Barcelona vs Real Madrid (26/10/2025) 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="C59" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET CR - 60 
- Partidos de Ida semifinales Central American Cup (21/10/2025 - 23/10/2025) 
+      <c r="C59" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - DORADOBET PE - 15 
+ https://doradobet.com/pe/new-casino/categoria/tragamonedas-4 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
       <c r="E59" s="5" t="n"/>
       <c r="G59" s="5" t="n"/>
-      <c r="I59" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET PE - 15 
- UFC 321- TomAspinall vs CirylGane (25/10/2025) 
-Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="K59" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET GT - 15 
- Liga española - Clasico Barcelona vs Real Madrid (26/10/2025) 
+      <c r="I59" s="5" t="n"/>
+      <c r="K59" s="26" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ECUABET - 30 
+ Cómo recargar  en ecuabet 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="C60" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - DORADOBET GT - 30 
- https://doradobet.com/gt/new-casino/categoria/tragamonedas-513                                 
-Responsable hacer: Juan Manuel 
+      <c r="C60" s="26" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - ECUABET - 15 
+ https://ecuabet.com/trabaja-con-nosotros 
+Responsable hacer: None 
  Responsable publicar: Santiago</t>
         </is>
       </c>
       <c r="E60" s="5" t="n"/>
       <c r="G60" s="5" t="n"/>
-      <c r="I60" s="30" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ECUABET - 15 
- Liga española: clasico Barcelona vs Real Madrid (26/10/25) 
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="K60" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET PE - 30 
- Liga española - Clasico Barcelona vs Real Madrid (26/10/2025) 
-Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
+      <c r="I60" s="5" t="n"/>
+      <c r="K60" s="5" t="n"/>
     </row>
     <row r="61">
-      <c r="C61" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - DORADOBET PE - 30 
- https://doradobet.com/pe/new-casino/categoria/tragamonedas-4 
+      <c r="C61" s="26" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ECUABET - 30 
+ Jornada 3 Champions League (21/10/2025 - 22/10/2025) 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
       <c r="E61" s="5" t="n"/>
       <c r="G61" s="5" t="n"/>
-      <c r="I61" s="30" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - ECUABET - 30 
- Cómo recargar  en ecuabet  
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="K61" s="30" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ECUABET - 30 
- Cómo recargar  en ecuabet 
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
+      <c r="I61" s="5" t="n"/>
+      <c r="K61" s="5" t="n"/>
     </row>
     <row r="62">
-      <c r="C62" s="30" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - ECUABET - 30 
- https://ecuabet.com/trabaja-con-nosotros 
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
+      <c r="C62" s="5" t="n"/>
       <c r="E62" s="5" t="n"/>
       <c r="G62" s="5" t="n"/>
       <c r="I62" s="5" t="n"/>
       <c r="K62" s="5" t="n"/>
     </row>
     <row r="63">
-      <c r="C63" s="30" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - ECUABET - 60 
- Jornada 3 Champions League (21/10/2025 - 22/10/2025) 
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
+      <c r="C63" s="5" t="n"/>
       <c r="E63" s="5" t="n"/>
       <c r="G63" s="5" t="n"/>
       <c r="I63" s="5" t="n"/>
       <c r="K63" s="5" t="n"/>
     </row>
     <row r="64">
-      <c r="C64" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - DORADOBET SV - 60 
- https://doradobet.sv/new-casino/proveedor/EREDTIGER 
-Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
+      <c r="C64" s="5" t="n"/>
       <c r="E64" s="5" t="n"/>
       <c r="G64" s="5" t="n"/>
       <c r="I64" s="5" t="n"/>
@@ -1870,12 +1611,12 @@
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>Lunes 27 (15m)</t>
+          <t>Lunes 27 (30m)</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Martes 28 (3h)</t>
+          <t>Martes 28 (1h 30m)</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -1885,7 +1626,7 @@
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>Jueves 30 (6h 15m)</t>
+          <t>Jueves 30 (1h)</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
@@ -1902,27 +1643,27 @@
       <c r="K73" s="11" t="n"/>
     </row>
     <row r="74">
-      <c r="C74" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET CR - 15 
+      <c r="C74" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET CR - 30 
  Partidos de vuelta semifinales Central American Cup (28/10/2025 - 30/10/2025) 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="E74" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET CR - 60 
+      <c r="E74" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET CR - 30 
  Juegos de casino rentables 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
       <c r="G74" s="5" t="n"/>
-      <c r="I74" s="26" t="inlineStr">
-        <is>
-          <t>Publicar - None - CAMANBET - 120 
- Semana 6/7/8/9 de NFL -2/10/2025 - 30/10/2025 
+      <c r="I74" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - DORADOBET CR - 15 
+ https://doradobet.com/new-casino/categoria/poker-540         
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
@@ -1931,19 +1672,19 @@
     </row>
     <row r="75">
       <c r="C75" s="5" t="n"/>
-      <c r="E75" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET GT - 60 
+      <c r="E75" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET GT - 30 
  Central American Cup - semifinales de vuelta (30/10/2025) 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
       <c r="G75" s="5" t="n"/>
-      <c r="I75" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - DORADOBET CR - 120 
- https://doradobet.com/new-casino/categoria/poker-540         
+      <c r="I75" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - DORADOBET GT - 15 
+ https://doradobet.com/gt/new-casino/proveedor/HIGH5GAMES                                 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
@@ -1952,19 +1693,19 @@
     </row>
     <row r="76">
       <c r="C76" s="5" t="n"/>
-      <c r="E76" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - DORADOBET GT - 60 
+      <c r="E76" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - DORADOBET GT - 30 
  Guía de juego Halloween Lotto 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
       <c r="G76" s="5" t="n"/>
-      <c r="I76" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - DORADOBET GT - 60 
- https://doradobet.com/gt/new-casino/proveedor/HIGH5GAMES                                 
+      <c r="I76" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - DORADOBET PE - 15 
+ https://doradobet.com/pe/politica-de-privacidad 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
@@ -1975,10 +1716,10 @@
       <c r="C77" s="5" t="n"/>
       <c r="E77" s="5" t="n"/>
       <c r="G77" s="5" t="n"/>
-      <c r="I77" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - DORADOBET PE - 15 
- https://doradobet.com/pe/politica-de-privacidad 
+      <c r="I77" s="26" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - ECUABET - 15 
+ https://ecuabet.com/politica-de-privacidad 
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
@@ -1989,28 +1730,14 @@
       <c r="C78" s="5" t="n"/>
       <c r="E78" s="5" t="n"/>
       <c r="G78" s="5" t="n"/>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - ECUABET - 30 
- https://ecuabet.com/politica-de-privacidad 
-Responsable hacer: Santiago 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
+      <c r="I78" s="5" t="n"/>
       <c r="K78" s="5" t="n"/>
     </row>
     <row r="79">
       <c r="C79" s="5" t="n"/>
       <c r="E79" s="5" t="n"/>
       <c r="G79" s="5" t="n"/>
-      <c r="I79" s="29" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - DORADOBET SV - 30 
- https://doradobet.sv/new-casino/categoria/blackjack-331 
-Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
+      <c r="I79" s="5" t="n"/>
       <c r="K79" s="5" t="n"/>
     </row>
     <row r="80">
@@ -2256,18 +1983,18 @@
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Miércoles 1 (4h)</t>
+          <t>Miércoles 1 (7h)</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Jueves 2 (5h 45m)</t>
+          <t>Jueves 2 (6h)</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>Viernes 3 (7h 45m)</t>
+          <t>Viernes 3 (6h)</t>
         </is>
       </c>
     </row>
@@ -2280,41 +2007,41 @@
     </row>
     <row r="4">
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="24" t="n"/>
+      <c r="D4" s="23" t="n"/>
       <c r="E4" s="5" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="26" t="inlineStr">
-        <is>
-          <t>Hacer - None - CAMANBET - 30 
+      <c r="F4" s="24" t="n"/>
+      <c r="G4" s="29" t="inlineStr">
+        <is>
+          <t>Hacer - None - CAMANBET - 60 
  https://camanbet.com/new-casino/proveedor/CALETA  
 Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
+ Responsable publicar: Manuela</t>
         </is>
       </c>
       <c r="H4" s="17" t="n"/>
-      <c r="I4" s="26" t="inlineStr">
-        <is>
-          <t>Hacer - None - CAMANBET - 90 
+      <c r="I4" s="29" t="inlineStr">
+        <is>
+          <t>Hacer - None - CAMANBET - 60 
  Ultima Fecha de la liga de venezuela 10/5/2025  
 Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="K4" s="26" t="inlineStr">
-        <is>
-          <t>Hacer - None - CAMANBET - 180 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="K4" s="29" t="inlineStr">
+        <is>
+          <t>Hacer - None - CAMANBET - 60 
  Guia para ganar con los Crash Games  
 Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
+ Responsable publicar: Manuela</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="28" t="n"/>
+      <c r="D5" s="27" t="n"/>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="28" t="n"/>
-      <c r="G5" s="29" t="inlineStr">
+      <c r="F5" s="27" t="n"/>
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>Hacer - Plataforma - DORADOBET CR - 60 
  https://doradobet.com/deportes/85                Golf  
@@ -2322,18 +2049,18 @@
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="H5" s="28" t="n"/>
-      <c r="I5" s="26" t="inlineStr">
-        <is>
-          <t>Hacer - None - CAMANBET - 120 
+      <c r="H5" s="27" t="n"/>
+      <c r="I5" s="29" t="inlineStr">
+        <is>
+          <t>Hacer - None - CAMANBET - 60 
  https://camanbet.com/deportes/68  
 Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="K5" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Plataforma - DORADOBET CR - 120 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="K5" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Plataforma - DORADOBET CR - 60 
  https://doradobet.com/new-casino/categoria/poker-540          
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
@@ -2342,27 +2069,27 @@
     </row>
     <row r="6">
       <c r="C6" s="5" t="n"/>
-      <c r="D6" s="28" t="n"/>
+      <c r="D6" s="27" t="n"/>
       <c r="E6" s="5" t="n"/>
-      <c r="F6" s="28" t="n"/>
-      <c r="G6" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - DORADOBET GT - 30 
+      <c r="F6" s="27" t="n"/>
+      <c r="G6" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - DORADOBET GT - 60 
  Liga de Guatemala - Comunicaciones vs Municipal y Antigua vs Xelajú (5/10/2025)  
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="H6" s="28" t="n"/>
-      <c r="I6" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Plataforma - DORADOBET CR - 15 
+      <c r="H6" s="27" t="n"/>
+      <c r="I6" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Plataforma - DORADOBET CR - 60 
  https://doradobet.com/new-casino/proveedor/PFBM  
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="K6" s="29" t="inlineStr">
+      <c r="K6" s="25" t="inlineStr">
         <is>
           <t>Hacer - Plataforma - DORADOBET GT - 60 
  https://doradobet.com/gt/new-casino/proveedor/HIGH5GAMES                                  
@@ -2373,27 +2100,27 @@
     </row>
     <row r="7">
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="28" t="n"/>
+      <c r="D7" s="27" t="n"/>
       <c r="E7" s="5" t="n"/>
-      <c r="F7" s="28" t="n"/>
-      <c r="G7" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Plataforma - DORADOBET GT - 15 
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Plataforma - DORADOBET GT - 60 
  https://doradobet.com/deportes/106                                        Fútbol Australiano  
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="H7" s="28" t="n"/>
-      <c r="I7" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Plataforma - DORADOBET GT - 30 
+      <c r="H7" s="27" t="n"/>
+      <c r="I7" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Plataforma - DORADOBET GT - 60 
  https://doradobet.com/gt/new-casino/categoria/tragamonedas-513                                  
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="K7" s="29" t="inlineStr">
+      <c r="K7" s="25" t="inlineStr">
         <is>
           <t>Hacer - Blog - DORADOBET PE - 60 
  Juegos de Playtech  
@@ -2404,10 +2131,10 @@
     </row>
     <row r="8">
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="28" t="n"/>
+      <c r="D8" s="27" t="n"/>
       <c r="E8" s="5" t="n"/>
-      <c r="F8" s="28" t="n"/>
-      <c r="G8" s="29" t="inlineStr">
+      <c r="F8" s="27" t="n"/>
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>Hacer - Blog - DORADOBET PE - 60 
  Liga 1 Perú - ADT vs Sporting Cristal (4/10/2025)  
@@ -2415,18 +2142,18 @@
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="H8" s="28" t="n"/>
-      <c r="I8" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Plataforma - DORADOBET PE - 30 
+      <c r="H8" s="27" t="n"/>
+      <c r="I8" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Plataforma - DORADOBET PE - 60 
  https://doradobet.com/pe/new-casino/categoria/tragamonedas-4  
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="K8" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Plataforma - DORADOBET PE - 15 
+      <c r="K8" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Plataforma - DORADOBET PE - 60 
  https://doradobet.com/pe/politica-de-privacidad  
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
@@ -2435,129 +2162,164 @@
     </row>
     <row r="9">
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="28" t="n"/>
+      <c r="D9" s="27" t="n"/>
       <c r="E9" s="5" t="n"/>
-      <c r="F9" s="28" t="n"/>
-      <c r="G9" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Plataforma - DORADOBET PE - 15 
+      <c r="F9" s="27" t="n"/>
+      <c r="G9" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Plataforma - DORADOBET PE - 60 
  https://doradobet.com/pe/new-casino/categoria/ruleta-11  
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="H9" s="28" t="n"/>
-      <c r="I9" s="29" t="inlineStr">
+      <c r="H9" s="27" t="n"/>
+      <c r="I9" s="26" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - ECUABET - 0 
+ Torneo deportivo 1 - Torneo E-sports (4/10/2025 - 30/10/2025)  
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="K9" s="26" t="inlineStr">
+        <is>
+          <t>Hacer - Plataforma - ECUABET - 0 
+ https://ecuabet.com/politica-de-privacidad  
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="27" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="27" t="n"/>
+      <c r="G10" s="26" t="inlineStr">
+        <is>
+          <t>Hacer - Plataforma - ECUABET - 0 
+ https://ecuabet.com/new-casino/categoria/populares-241  
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="H10" s="27" t="n"/>
+      <c r="I10" s="25" t="inlineStr">
         <is>
           <t>Hacer - Plataforma - DORADOBET SV - 60 
  https://doradobet.sv/new-casino/proveedor/EREDTIGER  
 Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="K9" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Plataforma - DORADOBET SV - 30 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="K10" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Plataforma - DORADOBET SV - 60 
  https://doradobet.sv/new-casino/categoria/blackjack-331  
 Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="28" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="28" t="n"/>
-      <c r="G10" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Plataforma - DORADOBET SV - 30 
- https://doradobet.sv/deportes/107        Hockey sobre césped  
-Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="H10" s="28" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="28" t="n"/>
+      <c r="D11" s="27" t="n"/>
       <c r="E11" s="5" t="n"/>
-      <c r="F11" s="28" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="28" t="n"/>
+      <c r="F11" s="27" t="n"/>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - ECUABET - 0 
+ Liga inglesa: Chelsea vs Liverpool (4/10/2025)  
+Responsable hacer: juan manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="H11" s="27" t="n"/>
       <c r="I11" s="5" t="n"/>
       <c r="K11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="28" t="n"/>
+      <c r="D12" s="27" t="n"/>
       <c r="E12" s="5" t="n"/>
-      <c r="F12" s="28" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="28" t="n"/>
+      <c r="F12" s="27" t="n"/>
+      <c r="G12" s="26" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - ECUABET - 0 
+ UFC 320 - Magomed Ankalaev - AlexPereira (4/10/2025)  
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="H12" s="27" t="n"/>
       <c r="I12" s="5" t="n"/>
       <c r="K12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="28" t="n"/>
+      <c r="D13" s="27" t="n"/>
       <c r="E13" s="5" t="n"/>
-      <c r="F13" s="28" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="28" t="n"/>
+      <c r="F13" s="27" t="n"/>
+      <c r="G13" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Plataforma - DORADOBET SV - 60 
+ https://doradobet.sv/deportes/107        Hockey sobre césped  
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="H13" s="27" t="n"/>
       <c r="I13" s="5" t="n"/>
       <c r="K13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="28" t="n"/>
+      <c r="D14" s="27" t="n"/>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="28" t="n"/>
+      <c r="F14" s="27" t="n"/>
       <c r="G14" s="5" t="n"/>
-      <c r="H14" s="28" t="n"/>
+      <c r="H14" s="27" t="n"/>
       <c r="I14" s="5" t="n"/>
       <c r="K14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="28" t="n"/>
+      <c r="D15" s="27" t="n"/>
       <c r="E15" s="5" t="n"/>
-      <c r="F15" s="28" t="n"/>
+      <c r="F15" s="27" t="n"/>
       <c r="G15" s="5" t="n"/>
-      <c r="H15" s="28" t="n"/>
+      <c r="H15" s="27" t="n"/>
       <c r="I15" s="5" t="n"/>
       <c r="K15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="28" t="n"/>
+      <c r="D16" s="27" t="n"/>
       <c r="E16" s="5" t="n"/>
-      <c r="F16" s="28" t="n"/>
+      <c r="F16" s="27" t="n"/>
       <c r="G16" s="5" t="n"/>
-      <c r="H16" s="28" t="n"/>
+      <c r="H16" s="27" t="n"/>
       <c r="I16" s="5" t="n"/>
       <c r="K16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="C17" s="5" t="n"/>
-      <c r="D17" s="28" t="n"/>
+      <c r="D17" s="27" t="n"/>
       <c r="E17" s="5" t="n"/>
-      <c r="F17" s="28" t="n"/>
+      <c r="F17" s="27" t="n"/>
       <c r="G17" s="5" t="n"/>
-      <c r="H17" s="28" t="n"/>
+      <c r="H17" s="27" t="n"/>
       <c r="I17" s="5" t="n"/>
       <c r="K17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="31" t="n"/>
+      <c r="D18" s="28" t="n"/>
       <c r="E18" s="5" t="n"/>
-      <c r="F18" s="31" t="n"/>
+      <c r="F18" s="28" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="28" t="n"/>
+      <c r="H18" s="27" t="n"/>
       <c r="I18" s="5" t="n"/>
       <c r="K18" s="5" t="n"/>
     </row>
@@ -2580,13 +2342,13 @@
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>Lunes 6 (1h 30m)</t>
+          <t>Lunes 6 (3h)</t>
         </is>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>Martes 7 (2h)</t>
+          <t>Martes 7 (4h)</t>
         </is>
       </c>
       <c r="F21" s="2" t="n"/>
@@ -2598,17 +2360,17 @@
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Jueves 9 (0h)</t>
+          <t>Jueves 9 (1h)</t>
         </is>
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>Viernes 10 (15m)</t>
+          <t>Viernes 10 (1h)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="29" t="inlineStr">
+      <c r="C22" s="25" t="inlineStr">
         <is>
           <t>Hacer - Blog - DORADOBET CR - 60 
  Guía de Super 7s  
@@ -2616,19 +2378,26 @@
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="E22" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - DORADOBET CR - 30 
+      <c r="E22" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - DORADOBET CR - 60 
  Honduras vs Costa Rica - Eliminatorias Concacaf (9/10/2025)  
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
       <c r="G22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="K22" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - DORADOBET CR - 15 
+      <c r="I22" s="26" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - ECUABET - 60 
+ Guía bingo online  
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="K22" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - DORADOBET CR - 60 
  Haití vs Costa Rica - Eliminatorias Concacaf (13/10/2025)  
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
@@ -2636,15 +2405,15 @@
       </c>
     </row>
     <row r="23">
-      <c r="C23" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - DORADOBET GT - 30 
+      <c r="C23" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - DORADOBET GT - 60 
  Eliminatorias Concacaf - Surinam vs Guatemala (10/10/2025)  
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="E23" s="29" t="inlineStr">
+      <c r="E23" s="25" t="inlineStr">
         <is>
           <t>Hacer - Blog - DORADOBET GT - 60 
  Guía de juegos Piggy Coins  
@@ -2657,10 +2426,17 @@
       <c r="K23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="C24" s="5" t="n"/>
-      <c r="E24" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - DORADOBET PE - 30 
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - ECUABET - 60 
+ Amistoso Estados Unidos vs Ecuador (10/10/25)  
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - DORADOBET PE - 60 
  Guía de BlackJack  
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
@@ -2672,7 +2448,14 @@
     </row>
     <row r="25">
       <c r="C25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
+      <c r="E25" s="26" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - ECUABET - 60 
+ Guía apuestas en Dota 2  
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
       <c r="G25" s="5" t="n"/>
       <c r="I25" s="5" t="n"/>
       <c r="K25" s="5" t="n"/>
@@ -2769,77 +2552,91 @@
       <c r="D38" s="2" t="n"/>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>Martes 14 (0h)</t>
+          <t>Martes 14 (1h)</t>
         </is>
       </c>
       <c r="F38" s="2" t="n"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Miércoles 15 (2h)</t>
+          <t>Miércoles 15 (1h)</t>
         </is>
       </c>
       <c r="H38" s="2" t="n"/>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>Jueves 16 (4h 30m)</t>
+          <t>Jueves 16 (3h)</t>
         </is>
       </c>
       <c r="K38" s="1" t="inlineStr">
         <is>
-          <t>Viernes 17 (1h 15m)</t>
+          <t>Viernes 17 (3h)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="C39" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - DORADOBET GT - 120 
+      <c r="C39" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - DORADOBET GT - 60 
  Eliminatorias Concacaf - El Salvador vs Guatemala (14/10/2025)  
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
       <c r="D39" s="9" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="G39" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - DORADOBET CR - 120 
+      <c r="E39" s="26" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - ECUABET - 60 
+ ¿Qué son los pronósticos en vivo?  
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="G39" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - DORADOBET CR - 60 
  Alajuelense vs Saprissa - Liga de Costa Rica (18/10/2025)  
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="I39" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - DORADOBET CR - 30 
+      <c r="I39" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - DORADOBET CR - 60 
  Inicio de temporada NBA (21/10/2025)  
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="K39" s="26" t="inlineStr">
-        <is>
-          <t>Hacer - None - CAMANBET - 15 
+      <c r="K39" s="29" t="inlineStr">
+        <is>
+          <t>Hacer - None - CAMANBET - 60 
  Inicio de temporada de la NBA - 10/21/2025  
 Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
+ Responsable publicar: Manuela</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="5" t="n"/>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - ECUABET - 60 
+ Amistoso México vs Ecuador (14/10/25)  
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
       <c r="D40" s="10" t="n"/>
       <c r="E40" s="5" t="n"/>
       <c r="G40" s="5" t="n"/>
-      <c r="I40" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - DORADOBET GT - 180 
+      <c r="I40" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - DORADOBET GT - 60 
  Central American Cup - semifinales de ida (21/10/2025 - 23/10/2025)  
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="K40" s="29" t="inlineStr">
+      <c r="K40" s="25" t="inlineStr">
         <is>
           <t>Hacer - Blog - DORADOBET CR - 60 
  Partidos de Ida semifinales Central American Cup (21/10/2025 - 23/10/2025)  
@@ -2853,7 +2650,7 @@
       <c r="D41" s="10" t="n"/>
       <c r="E41" s="5" t="n"/>
       <c r="G41" s="5" t="n"/>
-      <c r="I41" s="29" t="inlineStr">
+      <c r="I41" s="25" t="inlineStr">
         <is>
           <t>Hacer - Blog - DORADOBET PE - 60 
  Jornada 3 Champions League (21/10/2025 - 22/10/2025)  
@@ -2861,7 +2658,14 @@
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="K41" s="5" t="n"/>
+      <c r="K41" s="26" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - ECUABET - 60 
+ Jornada 3 Champions League (21/10/2025 - 22/10/2025)  
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="C42" s="5" t="n"/>
@@ -2973,56 +2777,56 @@
       <c r="D55" s="2" t="n"/>
       <c r="E55" s="1" t="inlineStr">
         <is>
-          <t>Martes 21 (30m)</t>
+          <t>Martes 21 (2h)</t>
         </is>
       </c>
       <c r="F55" s="2" t="n"/>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>Miércoles 22 (45m)</t>
+          <t>Miércoles 22 (3h)</t>
         </is>
       </c>
       <c r="H55" s="2" t="n"/>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Jueves 23 (2h 15m)</t>
+          <t>Jueves 23 (5h)</t>
         </is>
       </c>
       <c r="K55" s="1" t="inlineStr">
         <is>
-          <t>Viernes 24 (15m)</t>
+          <t>Viernes 24 (1h)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="C56" s="5" t="n"/>
-      <c r="E56" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - DORADOBET CR - 30 
+      <c r="E56" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - DORADOBET CR - 60 
  UFC 321- TomAspinall vs CirylGane (25/10/2025)  
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="G56" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - DORADOBET PE - 30 
+      <c r="G56" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - DORADOBET PE - 60 
  F1 - GP México (26/10/2025)  
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="I56" s="26" t="inlineStr">
+      <c r="I56" s="29" t="inlineStr">
         <is>
           <t>Hacer - None - CAMANBET - 60 
  Clasico Barcelona vs Real Madrid - Liga Española - 10/26/2025  
 Responsable hacer: Juan Manuel 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="K56" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - DORADOBET CR - 15 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="K56" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - DORADOBET CR - 60 
  Partidos de vuelta semifinales Central American Cup (28/10/2025 - 30/10/2025)  
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
@@ -3031,18 +2835,25 @@
     </row>
     <row r="57">
       <c r="C57" s="5" t="n"/>
-      <c r="E57" s="5" t="n"/>
-      <c r="G57" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - DORADOBET PE - 15 
+      <c r="E57" s="26" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - ECUABET - 60 
+ UFC 321- TomAspinall - CirylGane (25/10/2025)  
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="G57" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - DORADOBET PE - 60 
  UFC 321- TomAspinall vs CirylGane (25/10/2025)  
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
         </is>
       </c>
-      <c r="I57" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - DORADOBET GT - 30 
+      <c r="I57" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - DORADOBET GT - 60 
  F1 Gp México (26/10/2025)  
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
@@ -3053,10 +2864,17 @@
     <row r="58">
       <c r="C58" s="5" t="n"/>
       <c r="E58" s="5" t="n"/>
-      <c r="G58" s="5" t="n"/>
-      <c r="I58" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - DORADOBET GT - 15 
+      <c r="G58" s="26" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - ECUABET - 60 
+ Liga española: clasico Barcelona vs Real Madrid (26/10/25)  
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
+      <c r="I58" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - DORADOBET GT - 60 
  Liga española - Clasico Barcelona vs Real Madrid (26/10/2025)  
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
@@ -3068,9 +2886,9 @@
       <c r="C59" s="5" t="n"/>
       <c r="E59" s="5" t="n"/>
       <c r="G59" s="5" t="n"/>
-      <c r="I59" s="29" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - DORADOBET PE - 30 
+      <c r="I59" s="25" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - DORADOBET PE - 60 
  Liga española - Clasico Barcelona vs Real Madrid (26/10/2025)  
 Responsable hacer: Juan Manuel 
  Responsable publicar: Santiago</t>
@@ -3082,7 +2900,14 @@
       <c r="C60" s="5" t="n"/>
       <c r="E60" s="5" t="n"/>
       <c r="G60" s="5" t="n"/>
-      <c r="I60" s="5" t="n"/>
+      <c r="I60" s="26" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - ECUABET - 60 
+ Cómo recargar  en ecuabet  
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Santiago</t>
+        </is>
+      </c>
       <c r="K60" s="5" t="n"/>
     </row>
     <row r="61">
@@ -3195,7 +3020,7 @@
       <c r="K73" s="11" t="n"/>
     </row>
     <row r="74">
-      <c r="C74" s="29" t="inlineStr">
+      <c r="C74" s="25" t="inlineStr">
         <is>
           <t>Hacer - Blog - DORADOBET CR - 60 
  Juegos de casino rentables  
@@ -3209,7 +3034,7 @@
       <c r="K74" s="5" t="n"/>
     </row>
     <row r="75">
-      <c r="C75" s="29" t="inlineStr">
+      <c r="C75" s="25" t="inlineStr">
         <is>
           <t>Hacer - Blog - DORADOBET GT - 60 
  Central American Cup - semifinales de vuelta (30/10/2025)  
@@ -3223,7 +3048,7 @@
       <c r="K75" s="5" t="n"/>
     </row>
     <row r="76">
-      <c r="C76" s="29" t="inlineStr">
+      <c r="C76" s="25" t="inlineStr">
         <is>
           <t>Hacer - Blog - DORADOBET GT - 60 
  Guía de juego Halloween Lotto  
@@ -3495,20 +3320,20 @@
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="1" t="n"/>
       <c r="F2" s="2" t="n"/>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>Miércoles 1 (8h)</t>
+      <c r="G2" s="30" t="inlineStr">
+        <is>
+          <t>Miércoles 1 (10h 15m)</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Jueves 2 (2h 30m)</t>
+          <t>Jueves 2 (3h 30m)</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>Viernes 3 (3h)</t>
+          <t>Viernes 3 (5h)</t>
         </is>
       </c>
     </row>
@@ -3521,27 +3346,89 @@
     </row>
     <row r="4">
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="24" t="n"/>
+      <c r="D4" s="23" t="n"/>
       <c r="E4" s="5" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="27" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - ACIERTALA - 45 
+      <c r="F4" s="24" t="n"/>
+      <c r="G4" s="31" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - ACIERTALA - 60 
  ADT vs Sporting Cristal 10/4/2025 Liga 1 Perú  
 Responsable hacer: Manuela 
- Responsable publicar: Santiago</t>
+ Responsable publicar: Manuela</t>
         </is>
       </c>
       <c r="H4" s="17" t="n"/>
-      <c r="I4" s="27" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - ACIERTALA - 30 
+      <c r="I4" s="31" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ACIERTALA - 30 
+ ADT vs Sporting Cristal 10/4/2025 Liga 1 Perú 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="K4" s="31" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ACIERTALA - 30 
+ Partido Juventus vs AC Milán (Derby del Nord-Ovest) Liga Italiana 10/5/2025 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="27" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="27" t="n"/>
+      <c r="G5" s="31" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - ACIERTALA - 60 
+ Chelsea vs Liverpool Liga Inglesa 10/4/2025  
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="H5" s="27" t="n"/>
+      <c r="I5" s="31" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ACIERTALA - 30 
+ Chelsea vs Liverpool Liga Inglesa 10/4/2025 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="K5" s="29" t="inlineStr">
+        <is>
+          <t>Publicar - None - CAMANBET - 30 
+ Ultima Fecha de la liga de venezuela 10/5/2025 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="27" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="27" t="n"/>
+      <c r="G6" s="29" t="inlineStr">
+        <is>
+          <t>Publicar - None - CAMANBET - 15 
+ https://camanbet.com/deportes/67 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="H6" s="27" t="n"/>
+      <c r="I6" s="31" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - ACIERTALA - 60 
  ufc 320- Magomed Ankalaev -AlexPereira UFC 10/4/2025  
 Responsable hacer: Manuela 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="K4" s="32" t="inlineStr">
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="K6" s="32" t="inlineStr">
         <is>
           <t>Publicar - Blog - GANAPLAY GT - 30 
  5/10/2025 Comunicaciones vs Municipal Liga Guatemala (hablar de toda la jornada) 
@@ -3550,43 +3437,43 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="28" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="28" t="n"/>
-      <c r="G5" s="27" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - ACIERTALA - 120 
- Chelsea vs Liverpool Liga Inglesa 10/4/2025  
-Responsable hacer: Manuela 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="H5" s="28" t="n"/>
-      <c r="I5" s="27" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - ACIERTALA - 120 
- Partido Juventus vs AC Milán (Derby del Nord-Ovest) Liga Italiana 10/5/2025  
-Responsable hacer: Manuela 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="K5" s="32" t="inlineStr">
-        <is>
-          <t>Hacer - Plataforma - GANAPLAY GT - 30 
+    <row r="7">
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="27" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="29" t="inlineStr">
+        <is>
+          <t>Publicar - None - CAMANBET - 30 
+ Sorteo la Guardinga  
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="H7" s="27" t="n"/>
+      <c r="I7" s="31" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ACIERTALA - 30 
+ ufc 320- Magomed Ankalaev -AlexPereira UFC 10/4/2025 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="K7" s="32" t="inlineStr">
+        <is>
+          <t>Hacer - Plataforma - GANAPLAY GT - 60 
  https://ganaplay.gt/deportes/145  
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="28" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="28" t="n"/>
-      <c r="G6" s="32" t="inlineStr">
+    <row r="8">
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="27" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="27" t="n"/>
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>Publicar - Plataforma - GANAPLAY GT - 15 
  https://ganaplay.gt/deportes/67 
@@ -3594,60 +3481,19 @@
  Responsable publicar: Manuela</t>
         </is>
       </c>
-      <c r="H6" s="28" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="K6" s="32" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - GANAPLAY SV - 60 
+      <c r="H8" s="27" t="n"/>
+      <c r="I8" s="31" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - ACIERTALA - 60 
+ Partido Juventus vs AC Milán (Derby del Nord-Ovest) Liga Italiana 10/5/2025  
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="K8" s="32" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - GANAPLAY SV - 30 
  Partido Juventus vs AC Milán (Derby del Nord-Ovest) Liga Italiana 10/5/2025 
-Responsable hacer: Manuela 
- Responsable publicar: Manuela</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="28" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="28" t="n"/>
-      <c r="G7" s="32" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - GANAPLAY GT - 30 
- 5/10/2025 Comunicaciones vs Municipal Liga Guatemala (hablar de toda la jornada)  
-Responsable hacer: Manuela 
- Responsable publicar: Manuela</t>
-        </is>
-      </c>
-      <c r="H7" s="28" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="K7" s="32" t="inlineStr">
-        <is>
-          <t>Hacer - Plataforma - GANAPLAY SV - 15 
- https://ganaplay.sv/deportes/71  
-Responsable hacer: Manuela 
- Responsable publicar: Manuela</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="28" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="28" t="n"/>
-      <c r="G8" s="32" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - GANAPLAY GT - 15 
- Chelsea vs Liverpool 4/10/2025 Liga Inglesa   
-Responsable hacer: Manuela 
- Responsable publicar: Manuela</t>
-        </is>
-      </c>
-      <c r="H8" s="28" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="K8" s="32" t="inlineStr">
-        <is>
-          <t>Hacer - Plataforma - GANAPLAY SV - 30 
- https://ganaplay.sv/new-casino/categoria/ruleta-1587  
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
@@ -3655,23 +3501,23 @@
     </row>
     <row r="9">
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="28" t="n"/>
+      <c r="D9" s="27" t="n"/>
       <c r="E9" s="5" t="n"/>
-      <c r="F9" s="28" t="n"/>
+      <c r="F9" s="27" t="n"/>
       <c r="G9" s="32" t="inlineStr">
         <is>
-          <t>Publicar - Blog - GANAPLAY GT - 15 
- Chelsea vs Liverpool 4/10/2025 Liga Inglesa  
-Responsable hacer: Manuela 
- Responsable publicar: Manuela</t>
-        </is>
-      </c>
-      <c r="H9" s="28" t="n"/>
+          <t>Hacer - Blog - GANAPLAY GT - 60 
+ 5/10/2025 Comunicaciones vs Municipal Liga Guatemala (hablar de toda la jornada)  
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="H9" s="27" t="n"/>
       <c r="I9" s="5" t="n"/>
-      <c r="K9" s="33" t="inlineStr">
-        <is>
-          <t>Hacer - Plataforma - PANIPLAY - 15 
- https://paniplay.com/new-casino/proveedor/GAMEART  
+      <c r="K9" s="32" t="inlineStr">
+        <is>
+          <t>Hacer - Plataforma - GANAPLAY SV - 60 
+ https://ganaplay.sv/deportes/71  
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
@@ -3679,10 +3525,51 @@
     </row>
     <row r="10">
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="28" t="n"/>
+      <c r="D10" s="27" t="n"/>
       <c r="E10" s="5" t="n"/>
-      <c r="F10" s="28" t="n"/>
+      <c r="F10" s="27" t="n"/>
       <c r="G10" s="32" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - GANAPLAY GT - 60 
+ Chelsea vs Liverpool 4/10/2025 Liga Inglesa   
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="H10" s="27" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="K10" s="33" t="inlineStr">
+        <is>
+          <t>Hacer - Plataforma - PANIPLAY - 60 
+ https://paniplay.com/new-casino/proveedor/GAMEART  
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="27" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="27" t="n"/>
+      <c r="G11" s="32" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - GANAPLAY GT - 30 
+ Chelsea vs Liverpool 4/10/2025 Liga Inglesa  
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="H11" s="27" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="27" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="27" t="n"/>
+      <c r="G12" s="32" t="inlineStr">
         <is>
           <t>Publicar - Plataforma - GANAPLAY SV - 15 
  https://ganaplay.sv/promociones-bonos 
@@ -3690,16 +3577,16 @@
  Responsable publicar: Manuela</t>
         </is>
       </c>
-      <c r="H10" s="28" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="28" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="28" t="n"/>
-      <c r="G11" s="32" t="inlineStr">
+      <c r="H12" s="27" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="27" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="27" t="n"/>
+      <c r="G13" s="32" t="inlineStr">
         <is>
           <t>Publicar - Blog - GANAPLAY SV - 30 
  Aguila vs FAS (Clasico) Liga de El Salvador 10/4/2025 
@@ -3707,16 +3594,16 @@
  Responsable publicar: Manuela</t>
         </is>
       </c>
-      <c r="H11" s="28" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="28" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="28" t="n"/>
-      <c r="G12" s="32" t="inlineStr">
+      <c r="H13" s="27" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="27" t="n"/>
+      <c r="G14" s="32" t="inlineStr">
         <is>
           <t>Hacer - Blog - GANAPLAY SV - 60 
  Partido Juventus vs AC Milán (Derby del Nord-Ovest) Liga Italiana 10/5/2025  
@@ -3724,33 +3611,33 @@
  Responsable publicar: Manuela</t>
         </is>
       </c>
-      <c r="H12" s="28" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="28" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="28" t="n"/>
-      <c r="G13" s="32" t="inlineStr">
-        <is>
-          <t>Hacer - Plataforma - GANAPLAY SV - 30 
+      <c r="H14" s="27" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="27" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="27" t="n"/>
+      <c r="G15" s="32" t="inlineStr">
+        <is>
+          <t>Hacer - Plataforma - GANAPLAY SV - 60 
  https://ganaplay.sv/registro  
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
       </c>
-      <c r="H13" s="28" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="28" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="28" t="n"/>
-      <c r="G14" s="33" t="inlineStr">
+      <c r="H15" s="27" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="27" t="n"/>
+      <c r="G16" s="33" t="inlineStr">
         <is>
           <t>Publicar - Plataforma - PANIPLAY - 15 
  https://paniplay.com/new-casino/categoria/poker-540 
@@ -3758,61 +3645,41 @@
  Responsable publicar: Manuela</t>
         </is>
       </c>
-      <c r="H14" s="28" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="28" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="28" t="n"/>
-      <c r="G15" s="33" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - PANIPLAY - 60 
- ufc 320- Magomed Ankalaev -AlexPereira 10/4/2025 
-Responsable hacer: Manuela 
- Responsable publicar: Manuela</t>
-        </is>
-      </c>
-      <c r="H15" s="28" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="28" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="28" t="n"/>
-      <c r="G16" s="33" t="inlineStr">
-        <is>
-          <t>Hacer - Plataforma - PANIPLAY - 30 
- https://paniplay.com/deportes/146  
-Responsable hacer: Manuela 
- Responsable publicar: Manuela</t>
-        </is>
-      </c>
-      <c r="H16" s="28" t="n"/>
+      <c r="H16" s="27" t="n"/>
       <c r="I16" s="5" t="n"/>
       <c r="K16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="C17" s="5" t="n"/>
-      <c r="D17" s="28" t="n"/>
+      <c r="D17" s="27" t="n"/>
       <c r="E17" s="5" t="n"/>
-      <c r="F17" s="28" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="28" t="n"/>
+      <c r="F17" s="27" t="n"/>
+      <c r="G17" s="33" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - PANIPLAY - 30 
+ ufc 320- Magomed Ankalaev -AlexPereira 10/4/2025 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="H17" s="27" t="n"/>
       <c r="I17" s="5" t="n"/>
       <c r="K17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="31" t="n"/>
+      <c r="D18" s="28" t="n"/>
       <c r="E18" s="5" t="n"/>
-      <c r="F18" s="31" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="28" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="33" t="inlineStr">
+        <is>
+          <t>Hacer - Plataforma - PANIPLAY - 60 
+ https://paniplay.com/deportes/146  
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="H18" s="27" t="n"/>
       <c r="I18" s="5" t="n"/>
       <c r="K18" s="5" t="n"/>
     </row>
@@ -3822,7 +3689,14 @@
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="8" t="n"/>
-      <c r="G19" s="5" t="n"/>
+      <c r="G19" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - DORADOBET SV - 15 
+ https://doradobet.sv/new-casino/proveedor/PAHACKSAW 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
       <c r="H19" s="7" t="n"/>
       <c r="I19" s="5" t="n"/>
       <c r="K19" s="5" t="n"/>
@@ -3835,51 +3709,93 @@
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>Lunes 6 (4h)</t>
+          <t>Lunes 6 (5h 30m)</t>
         </is>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>Martes 7 (3h)</t>
+          <t>Martes 7 (4h 30m)</t>
         </is>
       </c>
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Miércoles 8 (1h 15m)</t>
+          <t>Miércoles 8 (2h 30m)</t>
         </is>
       </c>
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Jueves 9 (15m)</t>
+          <t>Jueves 9 (1h)</t>
         </is>
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>Viernes 10 (1h 45m)</t>
+          <t>Viernes 10 (4h)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="27" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - ACIERTALA - 30 
+      <c r="C22" s="31" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - ACIERTALA - 60 
  Guía para apostar en Esports  
 Responsable hacer: Manuela 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="E22" s="32" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - GANAPLAY GT - 30 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ACIERTALA - 30 
+ Guía para apostar en Esports 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="G22" s="31" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ACIERTALA - 30 
+ ¿Cómo hacer apuestas de básquet? 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="I22" s="32" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - GANAPLAY SV - 60 
+ El salvador vs Guatemala Eliminatorias concacaf 10/14/2025  
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="K22" s="29" t="inlineStr">
+        <is>
+          <t>Publicar - None - CAMANBET - 15 
+ https://camanbet.com/new-casino/categoria/Bingos-1441 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>Publicar - None - CAMANBET - 30 
+ Guia para ganar con los Crash Games 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="E23" s="32" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - GANAPLAY GT - 60 
  Cómo Leer las Cuotas y Saber si una Apuesta Vale la Pena  
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
       </c>
-      <c r="G22" s="32" t="inlineStr">
+      <c r="G23" s="32" t="inlineStr">
         <is>
           <t>Publicar - Blog - GANAPLAY GT - 30 
  Cómo Leer las Cuotas y Saber si una Apuesta Vale la Pena 
@@ -3887,25 +3803,18 @@
  Responsable publicar: Manuela</t>
         </is>
       </c>
-      <c r="I22" s="32" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - GANAPLAY SV - 15 
- El salvador vs Guatemala Eliminatorias concacaf 10/14/2025  
-Responsable hacer: Manuela 
- Responsable publicar: Manuela</t>
-        </is>
-      </c>
-      <c r="K22" s="32" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - GANAPLAY GT - 15 
+      <c r="I23" s="5" t="n"/>
+      <c r="K23" s="32" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - GANAPLAY GT - 60 
  Guía de Póker  
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="C23" s="32" t="inlineStr">
+    <row r="24">
+      <c r="C24" s="32" t="inlineStr">
         <is>
           <t>Hacer - Plataforma - GANAPLAY GT - 60 
  https://ganaplay.gt/new-casino/categoria/populares-1573  
@@ -3913,15 +3822,15 @@
  Responsable publicar: Manuela</t>
         </is>
       </c>
-      <c r="E23" s="32" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - GANAPLAY SV - 30 
+      <c r="E24" s="32" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - GANAPLAY SV - 60 
  El salvador vs Panamá Eliminatorias concacaf  10/10/2025  
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
       </c>
-      <c r="G23" s="33" t="inlineStr">
+      <c r="G24" s="33" t="inlineStr">
         <is>
           <t>Publicar - Blog - PANIPLAY - 30 
  ¿Cómo hacer apuestas de básquet? 
@@ -3929,18 +3838,18 @@
  Responsable publicar: Manuela</t>
         </is>
       </c>
-      <c r="I23" s="5" t="n"/>
-      <c r="K23" s="32" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - GANAPLAY GT - 30 
+      <c r="I24" s="5" t="n"/>
+      <c r="K24" s="32" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - GANAPLAY GT - 60 
  El salvador vs Guatemala  eliminatorias concacaf 14/10/2010  
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="C24" s="32" t="inlineStr">
+    <row r="25">
+      <c r="C25" s="32" t="inlineStr">
         <is>
           <t>Hacer - Plataforma - GANAPLAY SV - 60 
  https://ganaplay.sv/new-casino/categoria/nuevos-1583  
@@ -3948,7 +3857,7 @@
  Responsable publicar: Manuela</t>
         </is>
       </c>
-      <c r="E24" s="32" t="inlineStr">
+      <c r="E25" s="32" t="inlineStr">
         <is>
           <t>Publicar - Blog - GANAPLAY SV - 30 
  El salvador vs Panamá Eliminatorias concacaf  10/10/2025 
@@ -3956,16 +3865,16 @@
  Responsable publicar: Manuela</t>
         </is>
       </c>
-      <c r="G24" s="33" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - PANIPLAY - 15 
+      <c r="G25" s="33" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - PANIPLAY - 60 
  Honduras vs Costa Rica eliminatorias Concacaaf 10/13/2025  
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
       </c>
-      <c r="I24" s="5" t="n"/>
-      <c r="K24" s="32" t="inlineStr">
+      <c r="I25" s="5" t="n"/>
+      <c r="K25" s="32" t="inlineStr">
         <is>
           <t>Publicar - Blog - GANAPLAY GT - 30 
  El salvador vs Guatemala  eliminatorias concacaf 14/10/2010 
@@ -3974,75 +3883,75 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="C25" s="33" t="inlineStr">
-        <is>
-          <t>Hacer - Plataforma - PANIPLAY - 30 
- https://paniplay.com/deportes/145  
-Responsable hacer: Manuela 
- Responsable publicar: Manuela</t>
-        </is>
-      </c>
-      <c r="E25" s="33" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - PANIPLAY - 60 
- Nicaragua vs Honduras 10/9/2025 Eliminatorias concacaf 
-Responsable hacer: Manuela 
- Responsable publicar: Manuela</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="K25" s="32" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - GANAPLAY SV - 15 
- El salvador vs Guatemala Eliminatorias concacaf 10/14/2025 
-Responsable hacer: Manuela 
- Responsable publicar: Manuela</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
       <c r="C26" s="33" t="inlineStr">
         <is>
+          <t>Hacer - Plataforma - PANIPLAY - 60 
+ https://paniplay.com/deportes/145  
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="E26" s="33" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - PANIPLAY - 30 
+ Nicaragua vs Honduras 10/9/2025 Eliminatorias concacaf 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="K26" s="32" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - GANAPLAY SV - 30 
+ El salvador vs Guatemala Eliminatorias concacaf 10/14/2025 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" s="33" t="inlineStr">
+        <is>
           <t>Hacer - Blog - PANIPLAY - 60 
  Nicaragua vs Honduras 10/9/2025 Eliminatorias concacaf  
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
       </c>
-      <c r="E26" s="33" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - PANIPLAY - 30 
+      <c r="E27" s="33" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - PANIPLAY - 60 
  ¿Cómo hacer apuestas de básquet?  
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
       </c>
-      <c r="G26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="K26" s="33" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - PANIPLAY - 15 
- Honduras vs Costa Rica eliminatorias Concacaaf 10/13/2025 
-Responsable hacer: Manuela 
- Responsable publicar: Manuela</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
       <c r="I27" s="5" t="n"/>
-      <c r="K27" s="5" t="n"/>
+      <c r="K27" s="33" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - PANIPLAY - 30 
+ Honduras vs Costa Rica eliminatorias Concacaaf 10/13/2025 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="C28" s="5" t="n"/>
       <c r="E28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
       <c r="I28" s="5" t="n"/>
-      <c r="K28" s="5" t="n"/>
+      <c r="K28" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - DORADOBET SV - 15 
+ https://doradobet.sv/deportes/107        Hockey sobre césped 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="C29" s="5" t="n"/>
@@ -4109,7 +4018,7 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>Lunes 13 (15m)</t>
+          <t>Lunes 13 (30m)</t>
         </is>
       </c>
       <c r="D38" s="2" t="n"/>
@@ -4127,19 +4036,19 @@
       <c r="H38" s="2" t="n"/>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>Jueves 16 (2h 15m)</t>
+          <t>Jueves 16 (4h 30m)</t>
         </is>
       </c>
       <c r="K38" s="1" t="inlineStr">
         <is>
-          <t>Viernes 17 (6h 30m)</t>
+          <t>Viernes 17 (8h)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="C39" s="32" t="inlineStr">
         <is>
-          <t>Publicar - Blog - GANAPLAY GT - 15 
+          <t>Publicar - Blog - GANAPLAY GT - 30 
  Guía de Póker 
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
@@ -4147,26 +4056,26 @@
       </c>
       <c r="D39" s="9" t="n"/>
       <c r="E39" s="5" t="n"/>
-      <c r="G39" s="27" t="inlineStr">
+      <c r="G39" s="31" t="inlineStr">
         <is>
           <t>Hacer - Blog - ACIERTALA - 60 
  Inicio de temporada de NBA 21/10/2025  
 Responsable hacer: Manuela 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="I39" s="27" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - ACIERTALA - 15 
- Jornada 3 Champions 21-22 10/23/2025  
-Responsable hacer: Manuela 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="K39" s="32" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - GANAPLAY GT - 60 
- Central American Cup 21/10/2025 - 23/10/2025 semifinales ida  
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="I39" s="31" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ACIERTALA - 30 
+ Inicio de temporada de NBA 21/10/2025 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="K39" s="31" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ACIERTALA - 30 
+ Jornada 3 Champions 21-22 10/23/2025 
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
@@ -4177,18 +4086,18 @@
       <c r="D40" s="10" t="n"/>
       <c r="E40" s="5" t="n"/>
       <c r="G40" s="5" t="n"/>
-      <c r="I40" s="32" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - GANAPLAY SV - 30 
- Inicio de temporada de NBA 10/21/2025  
+      <c r="I40" s="31" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - ACIERTALA - 60 
+ Jornada 3 Champions 21-22 10/23/2025  
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
       </c>
       <c r="K40" s="32" t="inlineStr">
         <is>
-          <t>Hacer - Blog - GANAPLAY GT - 30 
- Inicio de temporada NBA 10/21/2025  
+          <t>Hacer - Blog - GANAPLAY GT - 60 
+ Central American Cup 21/10/2025 - 23/10/2025 semifinales ida  
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
@@ -4199,18 +4108,18 @@
       <c r="D41" s="10" t="n"/>
       <c r="E41" s="5" t="n"/>
       <c r="G41" s="5" t="n"/>
-      <c r="I41" s="33" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - PANIPLAY - 30 
- Jornada 14 liga de honduras (Olimpia vs motagua) 10/21/2025  
+      <c r="I41" s="32" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - GANAPLAY SV - 60 
+ Inicio de temporada de NBA 10/21/2025  
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
       </c>
       <c r="K41" s="32" t="inlineStr">
         <is>
-          <t>Publicar - Blog - GANAPLAY GT - 30 
- Inicio de temporada NBA 10/21/2025 
+          <t>Hacer - Blog - GANAPLAY GT - 60 
+ Inicio de temporada NBA 10/21/2025  
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
@@ -4224,15 +4133,15 @@
       <c r="I42" s="33" t="inlineStr">
         <is>
           <t>Hacer - Blog - PANIPLAY - 60 
- Central American Cup Semis ida y vuelta 21/10/2025 - 23/10/2025  
+ Jornada 14 liga de honduras (Olimpia vs motagua) 10/21/2025  
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
       </c>
       <c r="K42" s="32" t="inlineStr">
         <is>
-          <t>Publicar - Blog - GANAPLAY SV - 30 
- Inicio de temporada de NBA 10/21/2025 
+          <t>Publicar - Blog - GANAPLAY GT - 30 
+ Inicio de temporada NBA 10/21/2025 
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
@@ -4243,11 +4152,18 @@
       <c r="D43" s="10" t="n"/>
       <c r="E43" s="5" t="n"/>
       <c r="G43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
+      <c r="I43" s="33" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - PANIPLAY - 60 
+ Central American Cup Semis ida y vuelta 21/10/2025 - 23/10/2025  
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
       <c r="K43" s="32" t="inlineStr">
         <is>
-          <t>Hacer - Blog - GANAPLAY SV - 60 
- Jornada 3 Champions 21-22 10/23/2025  
+          <t>Publicar - Blog - GANAPLAY SV - 30 
+ Inicio de temporada de NBA 10/21/2025 
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
@@ -4261,8 +4177,8 @@
       <c r="I44" s="5" t="n"/>
       <c r="K44" s="32" t="inlineStr">
         <is>
-          <t>Hacer - Blog - GANAPLAY SV - 30 
- Central American Cup Semis ida 21/10/2025 - 23/10/2025  
+          <t>Hacer - Blog - GANAPLAY SV - 60 
+ Jornada 3 Champions 21-22 10/23/2025  
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
@@ -4274,10 +4190,10 @@
       <c r="E45" s="5" t="n"/>
       <c r="G45" s="5" t="n"/>
       <c r="I45" s="5" t="n"/>
-      <c r="K45" s="33" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - PANIPLAY - 30 
- Jornada 14 liga de honduras (Olimpia vs motagua) 10/21/2025 
+      <c r="K45" s="32" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - GANAPLAY SV - 60 
+ Central American Cup Semis ida 21/10/2025 - 23/10/2025  
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
@@ -4291,8 +4207,8 @@
       <c r="I46" s="5" t="n"/>
       <c r="K46" s="33" t="inlineStr">
         <is>
-          <t>Publicar - Blog - PANIPLAY - 60 
- Central American Cup Semis ida y vuelta 21/10/2025 - 23/10/2025 
+          <t>Publicar - Blog - PANIPLAY - 30 
+ Jornada 14 liga de honduras (Olimpia vs motagua) 10/21/2025 
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
@@ -4306,8 +4222,8 @@
       <c r="I47" s="5" t="n"/>
       <c r="K47" s="33" t="inlineStr">
         <is>
-          <t>Hacer - Blog - PANIPLAY - 30 
- Inicio de temporada de NBA 10/21/2025  
+          <t>Publicar - Blog - PANIPLAY - 30 
+ Central American Cup Semis ida y vuelta 21/10/2025 - 23/10/2025 
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
@@ -4321,8 +4237,8 @@
       <c r="I48" s="5" t="n"/>
       <c r="K48" s="33" t="inlineStr">
         <is>
-          <t>Publicar - Blog - PANIPLAY - 30 
- Inicio de temporada de NBA 10/21/2025 
+          <t>Hacer - Blog - PANIPLAY - 60 
+ Inicio de temporada de NBA 10/21/2025  
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
@@ -4334,7 +4250,14 @@
       <c r="E49" s="5" t="n"/>
       <c r="G49" s="5" t="n"/>
       <c r="I49" s="5" t="n"/>
-      <c r="K49" s="5" t="n"/>
+      <c r="K49" s="33" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - PANIPLAY - 30 
+ Inicio de temporada de NBA 10/21/2025 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="C50" s="5" t="n"/>
@@ -4376,87 +4299,87 @@
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>Lunes 20 (4h)</t>
+          <t>Lunes 20 (3h 30m)</t>
         </is>
       </c>
       <c r="D55" s="2" t="n"/>
       <c r="E55" s="1" t="inlineStr">
         <is>
-          <t>Martes 21 (1h 30m)</t>
+          <t>Martes 21 (3h)</t>
         </is>
       </c>
       <c r="F55" s="2" t="n"/>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>Miércoles 22 (3h 15m)</t>
+          <t>Miércoles 22 (5h)</t>
         </is>
       </c>
       <c r="H55" s="2" t="n"/>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Jueves 23 (2h 15m)</t>
+          <t>Jueves 23 (3h 30m)</t>
         </is>
       </c>
       <c r="K55" s="1" t="inlineStr">
         <is>
-          <t>Viernes 24 (2h 15m)</t>
+          <t>Viernes 24 (3h 30m)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="C56" s="32" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - GANAPLAY GT - 30 
- https://ganaplay.gt/deportes/145 
-Responsable hacer: Manuela 
- Responsable publicar: Manuela</t>
-        </is>
-      </c>
-      <c r="E56" s="27" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - ACIERTALA - 45 
+      <c r="C56" s="29" t="inlineStr">
+        <is>
+          <t>Publicar - None - CAMANBET - 15 
+ https://camanbet.com/new-casino/proveedor/CALETA 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="E56" s="31" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - ACIERTALA - 60 
  Guí de blackjack  
 Responsable hacer: Manuela 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="G56" s="27" t="inlineStr">
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="G56" s="31" t="inlineStr">
         <is>
           <t>Hacer - Blog - ACIERTALA - 60 
  26/10/2025 Clasico Barcelona vs Real Madrid Liga española  
 Responsable hacer: Manuela 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="I56" s="27" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - ACIERTALA - 90 
- Gp de México F1 10/26/2025  
-Responsable hacer: Manuela 
- Responsable publicar: Santiago</t>
-        </is>
-      </c>
-      <c r="K56" s="32" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - GANAPLAY GT - 30 
- Vuelta semifinales centro american cup 28/10/2025 - 30/10/2025  
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="I56" s="31" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ACIERTALA - 30 
+ Guí de blackjack 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="K56" s="31" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ACIERTALA - 30 
+ Gp de México F1 10/26/2025 
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="C57" s="32" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - GANAPLAY GT - 60 
- Central American Cup 21/10/2025 - 23/10/2025 semifinales ida 
-Responsable hacer: Manuela 
+      <c r="C57" s="29" t="inlineStr">
+        <is>
+          <t>Publicar - None - CAMANBET - 30 
+ Inicio de temporada de la NBA - 10/21/2025 
+Responsable hacer: Juan Manuel 
  Responsable publicar: Manuela</t>
         </is>
       </c>
       <c r="E57" s="32" t="inlineStr">
         <is>
-          <t>Hacer - Blog - GANAPLAY SV - 15 
+          <t>Hacer - Blog - GANAPLAY SV - 60 
  Clasico Barcelona vs Real Madrid Liga española 10/26/2025  
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
@@ -4464,25 +4387,25 @@
       </c>
       <c r="G57" s="32" t="inlineStr">
         <is>
-          <t>Hacer - Blog - GANAPLAY GT - 15 
+          <t>Hacer - Blog - GANAPLAY GT - 60 
  26/10/2025 Clasico Barcelona vs Real Madrid  
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
       </c>
-      <c r="I57" s="32" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - GANAPLAY GT - 15 
- 26/10/2025 Clasico Barcelona vs Real Madrid 
-Responsable hacer: Manuela 
- Responsable publicar: Manuela</t>
-        </is>
-      </c>
-      <c r="K57" s="32" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - GANAPLAY SV - 60 
- Central American Cup Semis vuelta y repechaje 28/10/2025 - 30/10/2025 
-Responsable hacer: Manuela 
+      <c r="I57" s="31" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - ACIERTALA - 30 
+ 26/10/2025 Clasico Barcelona vs Real Madrid Liga española 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="K57" s="29" t="inlineStr">
+        <is>
+          <t>Publicar - None - CAMANBET - 30 
+ Clasico Barcelona vs Real Madrid - Liga Española - 10/26/2025 
+Responsable hacer: Juan Manuel 
  Responsable publicar: Manuela</t>
         </is>
       </c>
@@ -4490,65 +4413,135 @@
     <row r="58">
       <c r="C58" s="32" t="inlineStr">
         <is>
+          <t>Publicar - Plataforma - GANAPLAY GT - 15 
+ https://ganaplay.gt/deportes/145 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="E58" s="32" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - GANAPLAY SV - 60 
+ FAS vs Alianza Liga de El Salvador 10/25/2025  
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="G58" s="32" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - GANAPLAY SV - 30 
+ Clasico Barcelona vs Real Madrid Liga española 10/26/2025 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="I58" s="31" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - ACIERTALA - 60 
+ Gp de México F1 10/26/2025  
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="K58" s="32" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - GANAPLAY GT - 60 
+ Vuelta semifinales centro american cup 28/10/2025 - 30/10/2025  
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" s="32" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - GANAPLAY GT - 30 
+ Central American Cup 21/10/2025 - 23/10/2025 semifinales ida 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n"/>
+      <c r="G59" s="32" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - GANAPLAY SV - 30 
+ FAS vs Alianza Liga de El Salvador 10/25/2025 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="I59" s="32" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - GANAPLAY GT - 30 
+ 26/10/2025 Clasico Barcelona vs Real Madrid 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="K59" s="32" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - GANAPLAY SV - 30 
+ Central American Cup Semis vuelta y repechaje 28/10/2025 - 30/10/2025 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" s="32" t="inlineStr">
+        <is>
           <t>Publicar - Plataforma - GANAPLAY SV - 15 
  https://ganaplay.sv/deportes/71 
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
       </c>
-      <c r="E58" s="32" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - GANAPLAY SV - 30 
- FAS vs Alianza Liga de El Salvador 10/25/2025  
-Responsable hacer: Manuela 
- Responsable publicar: Manuela</t>
-        </is>
-      </c>
-      <c r="G58" s="32" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - GANAPLAY SV - 15 
- Clasico Barcelona vs Real Madrid Liga española 10/26/2025 
-Responsable hacer: Manuela 
- Responsable publicar: Manuela</t>
-        </is>
-      </c>
-      <c r="I58" s="33" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - PANIPLAY - 30 
+      <c r="E60" s="5" t="n"/>
+      <c r="G60" s="32" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - GANAPLAY SV - 60 
+ Central American Cup Semis vuelta y repechaje 28/10/2025 - 30/10/2025  
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="I60" s="33" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - PANIPLAY - 60 
  Clasico Barcelona vs Real Madrid 10/26/2025 Liga española  
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
       </c>
-      <c r="K58" s="33" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - PANIPLAY - 15 
+      <c r="K60" s="33" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - PANIPLAY - 30 
  Pagos anticipados paniplay, siempre 
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="C59" s="32" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - GANAPLAY SV - 30 
+    <row r="61">
+      <c r="C61" s="32" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - GANAPLAY SV - 15 
  https://ganaplay.sv/new-casino/categoria/ruleta-1587 
-Responsable hacer: Manuela 
- Responsable publicar: Manuela</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="n"/>
-      <c r="G59" s="32" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - GANAPLAY SV - 30 
- FAS vs Alianza Liga de El Salvador 10/25/2025 
-Responsable hacer: Manuela 
- Responsable publicar: Manuela</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="n"/>
-      <c r="K59" s="33" t="inlineStr">
+Responsable hacer: None 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n"/>
+      <c r="G61" s="33" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - PANIPLAY - 60 
+ Pagos anticipados paniplay, siempre  
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="n"/>
+      <c r="K61" s="33" t="inlineStr">
         <is>
           <t>Publicar - Blog - PANIPLAY - 30 
  Clasico Barcelona vs Real Madrid 10/26/2025 Liga española 
@@ -4557,53 +4550,11 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="C60" s="32" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - GANAPLAY SV - 60 
+    <row r="62">
+      <c r="C62" s="32" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - GANAPLAY SV - 30 
  Jornada 3 Champions 21-22 10/23/2025 
-Responsable hacer: Manuela 
- Responsable publicar: Manuela</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="n"/>
-      <c r="G60" s="32" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - GANAPLAY SV - 60 
- Central American Cup Semis vuelta y repechaje 28/10/2025 - 30/10/2025  
-Responsable hacer: Manuela 
- Responsable publicar: Manuela</t>
-        </is>
-      </c>
-      <c r="I60" s="5" t="n"/>
-      <c r="K60" s="5" t="n"/>
-    </row>
-    <row r="61">
-      <c r="C61" s="32" t="inlineStr">
-        <is>
-          <t>Publicar - Blog - GANAPLAY SV - 30 
- Central American Cup Semis ida 21/10/2025 - 23/10/2025 
-Responsable hacer: Manuela 
- Responsable publicar: Manuela</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="n"/>
-      <c r="G61" s="33" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - PANIPLAY - 15 
- Pagos anticipados paniplay, siempre  
-Responsable hacer: Manuela 
- Responsable publicar: Manuela</t>
-        </is>
-      </c>
-      <c r="I61" s="5" t="n"/>
-      <c r="K61" s="5" t="n"/>
-    </row>
-    <row r="62">
-      <c r="C62" s="33" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - PANIPLAY - 15 
- https://paniplay.com/new-casino/proveedor/GAMEART 
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
@@ -4614,21 +4565,42 @@
       <c r="K62" s="5" t="n"/>
     </row>
     <row r="63">
-      <c r="C63" s="5" t="n"/>
+      <c r="C63" s="32" t="inlineStr">
+        <is>
+          <t>Publicar - Blog - GANAPLAY SV - 30 
+ Central American Cup Semis ida 21/10/2025 - 23/10/2025 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
       <c r="E63" s="5" t="n"/>
       <c r="G63" s="5" t="n"/>
       <c r="I63" s="5" t="n"/>
       <c r="K63" s="5" t="n"/>
     </row>
     <row r="64">
-      <c r="C64" s="5" t="n"/>
+      <c r="C64" s="33" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - PANIPLAY - 15 
+ https://paniplay.com/new-casino/proveedor/GAMEART 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n"/>
       <c r="G64" s="5" t="n"/>
       <c r="I64" s="5" t="n"/>
       <c r="K64" s="5" t="n"/>
     </row>
     <row r="65">
-      <c r="C65" s="5" t="n"/>
+      <c r="C65" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - DORADOBET SV - 15 
+ https://doradobet.sv/new-casino/proveedor/EREDTIGER 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n"/>
       <c r="G65" s="5" t="n"/>
       <c r="I65" s="5" t="n"/>
@@ -4682,7 +4654,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Martes 28 (45m)</t>
+          <t>Martes 28 (1h)</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -4692,7 +4664,7 @@
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>Jueves 30 (2h 30m)</t>
+          <t>Jueves 30 (1h 30m)</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
@@ -4717,20 +4689,20 @@
  Responsable publicar: Manuela</t>
         </is>
       </c>
-      <c r="E74" s="27" t="inlineStr">
-        <is>
-          <t>Hacer - Blog - ACIERTALA - 45 
+      <c r="E74" s="31" t="inlineStr">
+        <is>
+          <t>Hacer - Blog - ACIERTALA - 60 
  ¿Cómo hacer apuestas de básquet?  
 Responsable hacer: Manuela 
- Responsable publicar: Santiago</t>
+ Responsable publicar: Manuela</t>
         </is>
       </c>
       <c r="G74" s="5" t="n"/>
-      <c r="I74" s="32" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - GANAPLAY GT - 60 
- https://ganaplay.gt/new-casino/categoria/populares-1573 
-Responsable hacer: Manuela 
+      <c r="I74" s="29" t="inlineStr">
+        <is>
+          <t>Publicar - None - CAMANBET - 30 
+ Semana 6/7/8/9 de NFL -2/10/2025 - 30/10/2025 
+Responsable hacer: Juan Manuel 
  Responsable publicar: Manuela</t>
         </is>
       </c>
@@ -4742,8 +4714,8 @@
       <c r="G75" s="5" t="n"/>
       <c r="I75" s="32" t="inlineStr">
         <is>
-          <t>Publicar - Plataforma - GANAPLAY SV - 60 
- https://ganaplay.sv/new-casino/categoria/nuevos-1583 
+          <t>Publicar - Plataforma - GANAPLAY GT - 15 
+ https://ganaplay.gt/new-casino/categoria/populares-1573 
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
@@ -4754,10 +4726,10 @@
       <c r="C76" s="5" t="n"/>
       <c r="E76" s="5" t="n"/>
       <c r="G76" s="5" t="n"/>
-      <c r="I76" s="33" t="inlineStr">
-        <is>
-          <t>Publicar - Plataforma - PANIPLAY - 30 
- https://paniplay.com/deportes/145 
+      <c r="I76" s="32" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - GANAPLAY SV - 15 
+ https://ganaplay.sv/new-casino/categoria/nuevos-1583 
 Responsable hacer: Manuela 
  Responsable publicar: Manuela</t>
         </is>
@@ -4768,14 +4740,28 @@
       <c r="C77" s="5" t="n"/>
       <c r="E77" s="5" t="n"/>
       <c r="G77" s="5" t="n"/>
-      <c r="I77" s="5" t="n"/>
+      <c r="I77" s="33" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - PANIPLAY - 15 
+ https://paniplay.com/deportes/145 
+Responsable hacer: Manuela 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
       <c r="K77" s="5" t="n"/>
     </row>
     <row r="78">
       <c r="C78" s="5" t="n"/>
       <c r="E78" s="5" t="n"/>
       <c r="G78" s="5" t="n"/>
-      <c r="I78" s="5" t="n"/>
+      <c r="I78" s="25" t="inlineStr">
+        <is>
+          <t>Publicar - Plataforma - DORADOBET SV - 15 
+ https://doradobet.sv/new-casino/categoria/blackjack-331 
+Responsable hacer: Juan Manuel 
+ Responsable publicar: Manuela</t>
+        </is>
+      </c>
       <c r="K78" s="5" t="n"/>
     </row>
     <row r="79">
